--- a/Bases de datos/clean/dic_arg_prev_dm.xlsx
+++ b/Bases de datos/clean/dic_arg_prev_dm.xlsx
@@ -489,7 +489,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>grupo_edad</t>
+          <t>grupo_edad_5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -504,19 +504,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20-24 años, 25-29 años, 30-34 años, 35-39 años, 40-44 años, 45-49 años, 50-54 años, 55-59 años, 60-64 años, 65-69 años, 70-74 años, 75-79 años, 80+ años</t>
+          <t>35-39, 40-44, 45-49, 50-54, 55-59, 60-64, 65-69, 70-74, 75-79, 80+</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>grupo_edad_10</t>
+          <t>sexo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Grupo de edad decenal</t>
+          <t>Sexo biológico</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -526,41 +526,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20-29 años, 30-39 años, 40-49 años, 50-59 años, 60-69 años, 70-79 años, 80+ años</t>
+          <t>Varón, Mujer</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sexo</t>
+          <t>dm_total</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sexo biológico</t>
+          <t>Total estimado de personas con diabetes mellitus por provincia, edad y sexo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Varón, Mujer</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dm_total</t>
+          <t>dm_total_se</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Total estimado de personas con diabetes mellitus por provincia, edad y sexo</t>
+          <t>Error estándar del total de personas con DM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dm_total_se</t>
+          <t>dm_total_cv</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Error estándar del total de personas con DM</t>
+          <t>Coeficiente de variación del total de personas con DM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -599,12 +599,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dm_total_cv</t>
+          <t>dm_prev</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Coeficiente de variación del total de personas con DM</t>
+          <t>Prevalencia de diabetes mellitus por autorreporte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dm_prev</t>
+          <t>dm_prev_se</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Prevalencia de diabetes mellitus por autorreporte</t>
+          <t>Error estándar del total de la prevalencia de personas con DM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dm_prev_se</t>
+          <t>dm_prev_cv</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Error estándar del total de la prevalencia de personas con DM</t>
+          <t>Coeficiente de variación de la prevalencia de personas con DM</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -665,22 +665,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dm_prev_cv</t>
+          <t>dm_prev_cv_cat</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Coeficiente de variación de la prevalencia de personas con DM</t>
+          <t>Categorización del coeficiente de variación de la prevalencia de personas con DM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Baja, Moderada, Alta, Muy alta</t>
         </is>
       </c>
     </row>

--- a/Bases de datos/clean/dic_arg_prev_dm.xlsx
+++ b/Bases de datos/clean/dic_arg_prev_dm.xlsx
@@ -438,19 +438,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Buenos Aires, CABA, Catamarca, Chaco, Chubut, Córdoba, Corrientes, Entre Ríos, Formosa, Jujuy, La Pampa, La Rioja, Mendoza, Misiones, Neuquén, Río Negro, Salta, San Juan, San Luis, Santa Cruz, Santa Fe, Santiago del Estero, Tierra del Fuego, Tucumán</t>
+          <t>NULL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>reg_id</t>
+          <t>grupo_edad_10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Identificador numérico de región estadística</t>
+          <t>Grupo de edad decenal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -460,19 +460,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1, 2, 3, 4, 5, 6</t>
+          <t>30-39, 40-49, 50-59, 60-69, 70-79, 80+</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>reg_nombre</t>
+          <t>sexo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Identificador categórico de región estadística</t>
+          <t>Sexo biológico</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -482,63 +482,63 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gran Buenos Aires, Pampeana, Noroeste, Noreste, Cuyo, Patagónica</t>
+          <t>Varón, Mujer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>grupo_edad_5</t>
+          <t>dm_total</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Grupo de edad quinquenal</t>
+          <t>Total estimado de personas con diabetes mellitus por provincia, edad y sexo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>35-39, 40-44, 45-49, 50-54, 55-59, 60-64, 65-69, 70-74, 75-79, 80+</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sexo</t>
+          <t>dm_total_se</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sexo biológico</t>
+          <t>Error estándar del total de personas con DM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Varón, Mujer</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dm_total</t>
+          <t>dm_total_cv</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Total estimado de personas con diabetes mellitus por provincia, edad y sexo</t>
+          <t>Coeficiente de variación del total de personas con DM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -555,12 +555,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dm_total_se</t>
+          <t>dm_prev</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Error estándar del total de personas con DM</t>
+          <t>Prevalencia de diabetes mellitus por autorreporte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dm_total_cv</t>
+          <t>dm_prev_se</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Coeficiente de variación del total de personas con DM</t>
+          <t>Error estándar del total de la prevalencia de personas con DM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -599,12 +599,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dm_prev</t>
+          <t>dm_prev_cv</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prevalencia de diabetes mellitus por autorreporte</t>
+          <t>Coeficiente de variación de la prevalencia de personas con DM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -621,39 +621,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dm_prev_se</t>
+          <t>dm_prev_cv_cat</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Error estándar del total de la prevalencia de personas con DM</t>
+          <t>Categorización del coeficiente de variación de la prevalencia de personas con DM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Baja, Moderada, Alta, Muy alta</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dm_prev_cv</t>
+          <t>dm2_total</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Coeficiente de variación de la prevalencia de personas con DM</t>
+          <t>Total estimado de personas de diabetes mellitus tipo 2 por autorreporte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -665,12 +665,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dm_prev_cv_cat</t>
+          <t>dm2_prev</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Categorización del coeficiente de variación de la prevalencia de personas con DM</t>
+          <t>Prevalencia de diabetes mellitus tipo 2 por autorreporte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Baja, Moderada, Alta, Muy alta</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
